--- a/artfynd/A 9186-2024 artfynd.xlsx
+++ b/artfynd/A 9186-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,12 +678,7 @@
         <v>96225931</v>
       </c>
       <c r="B2" t="n">
-        <v>93375</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96708</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -717,10 +712,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>556317.4974439711</v>
+        <v>556317</v>
       </c>
       <c r="R2" t="n">
-        <v>6310147.059553975</v>
+        <v>6310148</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -792,16 +787,11 @@
         <v>96225232</v>
       </c>
       <c r="B3" t="n">
-        <v>90653</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -830,10 +820,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>556335.3162678091</v>
+        <v>556336</v>
       </c>
       <c r="R3" t="n">
-        <v>6310163.6713224</v>
+        <v>6310163</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -899,6 +889,672 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>2400185</v>
+      </c>
+      <c r="B4" t="n">
+        <v>99035</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Hinsaryd, Sm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>556372</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6310093</v>
+      </c>
+      <c r="S4" t="n">
+        <v>25</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Nybro</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Bäckebo</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2005-07-10</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2005-07-10</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>skogsglänta</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Jörg Adelmann</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Jörg Adelmann</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>2858101</v>
+      </c>
+      <c r="B5" t="n">
+        <v>99153</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>219874</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Nattviol</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Platanthera bifolia</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Hinsaryd, Sm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>556372</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6310093</v>
+      </c>
+      <c r="S5" t="n">
+        <v>25</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Nybro</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Bäckebo</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2005-07-10</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2005-07-10</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>skogsglänta</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Jörg Adelmann</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Jörg Adelmann</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>96224873</v>
+      </c>
+      <c r="B6" t="n">
+        <v>97977</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>221944</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Lopplummer (aggregat)</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Huperzia selago agg.</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Hinsaryd göl, Sm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>556342</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6310257</v>
+      </c>
+      <c r="S6" t="n">
+        <v>25</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Nybro</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Bäckebo</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2021-09-21</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>14:39</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2021-09-21</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>14:39</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Thomas Strid</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Thomas Strid, Per Saarinen</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>96224875</v>
+      </c>
+      <c r="B7" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Hinsaryd göl, Sm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>556342</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6310257</v>
+      </c>
+      <c r="S7" t="n">
+        <v>25</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Nybro</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Bäckebo</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2021-09-21</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>14:39</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2021-09-21</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>14:39</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Thomas Strid</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Thomas Strid, Per Saarinen</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>106771067</v>
+      </c>
+      <c r="B8" t="n">
+        <v>97975</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>224361</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Äkta lopplummer</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Huperzia europaea</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Björk</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Hinsaryd göl, Sm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>556355</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6310255</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Nybro</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Bäckebo</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2021-09-21</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2021-09-21</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="inlineStr"/>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AP8" t="inlineStr">
+        <is>
+          <t>Stockholm-Naturhistoriska riksmuseet</t>
+        </is>
+      </c>
+      <c r="AR8" t="inlineStr">
+        <is>
+          <t>S22-4792</t>
+        </is>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Thomas Strid</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Göran Odelvik</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>106771066</v>
+      </c>
+      <c r="B9" t="n">
+        <v>97985</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>224363</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Vanlig revlummer</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum subsp. annotinum</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Hinsaryd göl, Sm</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>556355</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6310255</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Nybro</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Bäckebo</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2021-09-21</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2021-09-21</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF9" t="inlineStr"/>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AP9" t="inlineStr">
+        <is>
+          <t>Stockholm-Naturhistoriska riksmuseet</t>
+        </is>
+      </c>
+      <c r="AR9" t="inlineStr">
+        <is>
+          <t>S22-4796</t>
+        </is>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Thomas Strid</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Göran Odelvik</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 9186-2024 artfynd.xlsx
+++ b/artfynd/A 9186-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AZ9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -781,6 +786,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96225931</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -889,6 +899,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96225232</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1005,6 +1020,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/2400185</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1121,6 +1141,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/2858101</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1226,6 +1251,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96224873</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1335,6 +1365,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96224875</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1447,6 +1482,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106771067</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1555,8 +1595,23 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106771066</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>